--- a/output/pdf_financials_xlsx/IVC.H.xlsx
+++ b/output/pdf_financials_xlsx/IVC.H.xlsx
@@ -2113,46 +2113,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.062088</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.30982</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.412602</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.059158</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.864565</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.756578</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.657579</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.565195</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.457332</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.273248</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.181946</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.09407500000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.010905</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.01182</v>
       </c>
     </row>
     <row r="35">
@@ -2211,46 +2211,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.062088</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.30982</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.412602</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.059158</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.864565</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.756578</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.657579</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.565195</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.457332</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.273248</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.181946</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.09407500000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.010905</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.01182</v>
       </c>
     </row>
     <row r="37">
@@ -2799,46 +2799,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.112415</v>
+        <v>0.050327</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.312987</v>
+        <v>0.003167</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.414136</v>
+        <v>0.001534</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.074006</v>
+        <v>0.014848</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.8659750000000001</v>
+        <v>0.00141</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.757266</v>
+        <v>0.000688</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.659309</v>
+        <v>0.00173</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.56745</v>
+        <v>0.002255</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.459119</v>
+        <v>0.001787</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.274821</v>
+        <v>0.001573</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.184938</v>
+        <v>0.002992</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.096196</v>
+        <v>0.002121</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.014178</v>
+        <v>0.003273</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.018538</v>
+        <v>0.006718</v>
       </c>
     </row>
     <row r="49">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
